--- a/ingress-workflow_examples/animal/Dejana/OUL/metadata.xlsx
+++ b/ingress-workflow_examples/animal/Dejana/OUL/metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dejana\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Dejana\OULData\OUL_combined_mextracted\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB39BFA-DD5B-46AA-B1CA-C64D78FDAA7F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA191F7D-DF3E-4C1A-9784-CD3D8C7B7FBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28785" windowHeight="12165" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28790" windowHeight="12170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="animal" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="39">
   <si>
     <t>Animal</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>coh_4</t>
+  </si>
+  <si>
+    <t>847_2</t>
   </si>
 </sst>
 </file>
@@ -213,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -253,12 +256,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -406,14 +416,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMG50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AMG56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="1"/>
-    <col min="2" max="1021" width="10.140625" style="2"/>
+    <col min="1" max="1" width="10.1796875" style="1"/>
+    <col min="2" max="1021" width="10.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,7 +440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>378</v>
       </c>
@@ -447,7 +457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>379</v>
       </c>
@@ -464,7 +474,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>385</v>
       </c>
@@ -481,7 +491,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>387</v>
       </c>
@@ -498,7 +508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>388</v>
       </c>
@@ -515,7 +525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>304</v>
       </c>
@@ -532,7 +542,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>305</v>
       </c>
@@ -549,7 +559,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>381</v>
       </c>
@@ -566,7 +576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>382</v>
       </c>
@@ -583,7 +593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>383</v>
       </c>
@@ -600,7 +610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>384</v>
       </c>
@@ -617,7 +627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>527</v>
       </c>
@@ -634,7 +644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>528</v>
       </c>
@@ -651,7 +661,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>529</v>
       </c>
@@ -668,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>530</v>
       </c>
@@ -685,7 +695,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>531</v>
       </c>
@@ -702,7 +712,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>532</v>
       </c>
@@ -719,7 +729,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>533</v>
       </c>
@@ -736,7 +746,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>534</v>
       </c>
@@ -753,7 +763,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>535</v>
       </c>
@@ -770,7 +780,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>546</v>
       </c>
@@ -787,7 +797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>547</v>
       </c>
@@ -804,7 +814,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="14">
         <v>543</v>
       </c>
@@ -821,7 +831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="14">
         <v>544</v>
       </c>
@@ -838,7 +848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="14">
         <v>545</v>
       </c>
@@ -855,7 +865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="14">
         <v>647</v>
       </c>
@@ -872,7 +882,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="14">
         <v>648</v>
       </c>
@@ -889,7 +899,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>160</v>
       </c>
@@ -906,7 +916,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>161</v>
       </c>
@@ -923,7 +933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>162</v>
       </c>
@@ -940,7 +950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>163</v>
       </c>
@@ -957,7 +967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>116</v>
       </c>
@@ -974,7 +984,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>117</v>
       </c>
@@ -991,7 +1001,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>118</v>
       </c>
@@ -1008,7 +1018,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>119</v>
       </c>
@@ -1025,7 +1035,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>120</v>
       </c>
@@ -1042,7 +1052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>121</v>
       </c>
@@ -1059,7 +1069,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>136</v>
       </c>
@@ -1076,7 +1086,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>137</v>
       </c>
@@ -1093,7 +1103,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>206</v>
       </c>
@@ -1110,7 +1120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>207</v>
       </c>
@@ -1127,7 +1137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>210</v>
       </c>
@@ -1144,7 +1154,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>211</v>
       </c>
@@ -1161,7 +1171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>666</v>
       </c>
@@ -1178,7 +1188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>667</v>
       </c>
@@ -1195,7 +1205,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>668</v>
       </c>
@@ -1212,7 +1222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>669</v>
       </c>
@@ -1229,7 +1239,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>670</v>
       </c>
@@ -1246,7 +1256,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>671</v>
       </c>
@@ -1263,9 +1273,97 @@
         <v>8</v>
       </c>
     </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="8">
+        <v>845</v>
+      </c>
+      <c r="B51" s="2">
+        <v>16</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" s="8">
+        <v>846</v>
+      </c>
+      <c r="B52" s="2">
+        <v>16</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="8">
+        <v>847</v>
+      </c>
+      <c r="B53" s="2">
+        <v>16</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="8">
+        <v>19103</v>
+      </c>
+      <c r="B54" s="2">
+        <v>17</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="8">
+        <v>19105</v>
+      </c>
+      <c r="B55" s="2">
+        <v>17</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.05277777777778" bottom="1.05277777777778" header="0.78750000000000009" footer="0.78750000000000009"/>
-  <pageSetup firstPageNumber="4294967295" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup firstPageNumber="4294967295" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
@@ -1275,14 +1373,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J148"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J163"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="10.42578125" style="2"/>
-    <col min="3" max="3" width="24.140625" style="2" customWidth="1"/>
+    <col min="1" max="2" width="10.453125" style="2"/>
+    <col min="3" max="3" width="24.1796875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1298,12 +1396,12 @@
       <c r="E1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="17">
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="19">
         <v>378</v>
       </c>
       <c r="B2" s="2">
@@ -1316,8 +1414,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="19"/>
       <c r="B3" s="2">
         <v>1</v>
       </c>
@@ -1328,8 +1426,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="19"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -1340,8 +1438,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="17">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="19">
         <v>379</v>
       </c>
       <c r="B5" s="2">
@@ -1354,8 +1452,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="19"/>
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -1366,8 +1464,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="19"/>
       <c r="B7" s="2">
         <v>2</v>
       </c>
@@ -1378,8 +1476,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="17">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="19">
         <v>385</v>
       </c>
       <c r="B8" s="2">
@@ -1392,8 +1490,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="19"/>
       <c r="B9" s="2">
         <v>1</v>
       </c>
@@ -1404,8 +1502,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="19"/>
       <c r="B10" s="2">
         <v>2</v>
       </c>
@@ -1416,8 +1514,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="17">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="19">
         <v>387</v>
       </c>
       <c r="B11" s="2">
@@ -1430,8 +1528,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="19"/>
       <c r="B12" s="2">
         <v>1</v>
       </c>
@@ -1442,8 +1540,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="19"/>
       <c r="B13" s="2">
         <v>2</v>
       </c>
@@ -1454,8 +1552,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="17">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="19">
         <v>388</v>
       </c>
       <c r="B14" s="2">
@@ -1468,8 +1566,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="19"/>
       <c r="B15" s="2">
         <v>1</v>
       </c>
@@ -1480,8 +1578,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="19"/>
       <c r="B16" s="2">
         <v>2</v>
       </c>
@@ -1492,8 +1590,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="19">
         <v>304</v>
       </c>
       <c r="B17" s="2">
@@ -1506,8 +1604,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="19"/>
       <c r="B18" s="2">
         <v>1</v>
       </c>
@@ -1518,8 +1616,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="19"/>
       <c r="B19" s="2">
         <v>2</v>
       </c>
@@ -1530,8 +1628,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="17">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="19">
         <v>305</v>
       </c>
       <c r="B20" s="2">
@@ -1544,8 +1642,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="19"/>
       <c r="B21" s="2">
         <v>1</v>
       </c>
@@ -1556,8 +1654,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="19"/>
       <c r="B22" s="2">
         <v>2</v>
       </c>
@@ -1568,8 +1666,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="17">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="19">
         <v>381</v>
       </c>
       <c r="B23" s="2">
@@ -1582,8 +1680,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="19"/>
       <c r="B24" s="2">
         <v>1</v>
       </c>
@@ -1594,8 +1692,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="19"/>
       <c r="B25" s="2">
         <v>2</v>
       </c>
@@ -1606,8 +1704,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="17">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="19">
         <v>382</v>
       </c>
       <c r="B26" s="2">
@@ -1620,8 +1718,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="19"/>
       <c r="B27" s="2">
         <v>1</v>
       </c>
@@ -1632,8 +1730,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="19"/>
       <c r="B28" s="2">
         <v>2</v>
       </c>
@@ -1644,8 +1742,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="17">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="19">
         <v>383</v>
       </c>
       <c r="B29" s="2">
@@ -1658,8 +1756,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="19"/>
       <c r="B30" s="2">
         <v>1</v>
       </c>
@@ -1670,8 +1768,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="19"/>
       <c r="B31" s="2">
         <v>2</v>
       </c>
@@ -1682,8 +1780,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="17">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="19">
         <v>384</v>
       </c>
       <c r="B32" s="2">
@@ -1696,8 +1794,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="19"/>
       <c r="B33" s="2">
         <v>1</v>
       </c>
@@ -1708,8 +1806,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="19"/>
       <c r="B34" s="2">
         <v>2</v>
       </c>
@@ -1720,8 +1818,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="17">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="19">
         <v>527</v>
       </c>
       <c r="B35" s="2">
@@ -1734,8 +1832,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="19"/>
       <c r="B36" s="2">
         <v>1</v>
       </c>
@@ -1746,8 +1844,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="19"/>
       <c r="B37" s="2">
         <v>2</v>
       </c>
@@ -1758,8 +1856,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="17">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="19">
         <v>528</v>
       </c>
       <c r="B38" s="2">
@@ -1772,8 +1870,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="17"/>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="19"/>
       <c r="B39" s="2">
         <v>1</v>
       </c>
@@ -1784,8 +1882,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="19"/>
       <c r="B40" s="2">
         <v>2</v>
       </c>
@@ -1796,8 +1894,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="17">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="19">
         <v>529</v>
       </c>
       <c r="B41" s="2">
@@ -1810,8 +1908,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="19"/>
       <c r="B42" s="2">
         <v>1</v>
       </c>
@@ -1822,8 +1920,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="19"/>
       <c r="B43" s="2">
         <v>2</v>
       </c>
@@ -1834,8 +1932,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="17">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="19">
         <v>530</v>
       </c>
       <c r="B44" s="2">
@@ -1848,8 +1946,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="19"/>
       <c r="B45" s="2">
         <v>1</v>
       </c>
@@ -1860,8 +1958,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="19"/>
       <c r="B46" s="2">
         <v>2</v>
       </c>
@@ -1872,8 +1970,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="17">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="19">
         <v>531</v>
       </c>
       <c r="B47" s="2">
@@ -1886,8 +1984,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="19"/>
       <c r="B48" s="2">
         <v>1</v>
       </c>
@@ -1898,8 +1996,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="19"/>
       <c r="B49" s="2">
         <v>2</v>
       </c>
@@ -1910,8 +2008,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="17">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="19">
         <v>532</v>
       </c>
       <c r="B50" s="2">
@@ -1924,8 +2022,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="17"/>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="19"/>
       <c r="B51" s="2">
         <v>1</v>
       </c>
@@ -1936,8 +2034,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="17"/>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="19"/>
       <c r="B52" s="2">
         <v>2</v>
       </c>
@@ -1948,8 +2046,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="17">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="19">
         <v>533</v>
       </c>
       <c r="B53" s="2">
@@ -1962,8 +2060,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="19"/>
       <c r="B54" s="2">
         <v>1</v>
       </c>
@@ -1974,8 +2072,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="19"/>
       <c r="B55" s="2">
         <v>2</v>
       </c>
@@ -1986,8 +2084,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="17">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="19">
         <v>534</v>
       </c>
       <c r="B56" s="2">
@@ -2000,8 +2098,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="17"/>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="19"/>
       <c r="B57" s="2">
         <v>1</v>
       </c>
@@ -2012,8 +2110,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="17"/>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="19"/>
       <c r="B58" s="2">
         <v>2</v>
       </c>
@@ -2024,8 +2122,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="17">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="19">
         <v>535</v>
       </c>
       <c r="B59" s="2">
@@ -2038,8 +2136,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="17"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="19"/>
       <c r="B60" s="2">
         <v>1</v>
       </c>
@@ -2050,8 +2148,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="17"/>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="19"/>
       <c r="B61" s="2">
         <v>2</v>
       </c>
@@ -2062,8 +2160,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="17">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="19">
         <v>546</v>
       </c>
       <c r="B62" s="2">
@@ -2076,8 +2174,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="17"/>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="19"/>
       <c r="B63" s="2">
         <v>1</v>
       </c>
@@ -2088,8 +2186,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="17"/>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="19"/>
       <c r="B64" s="2">
         <v>2</v>
       </c>
@@ -2100,8 +2198,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="17">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" s="19">
         <v>547</v>
       </c>
       <c r="B65" s="2">
@@ -2114,8 +2212,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="17"/>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" s="19"/>
       <c r="B66" s="2">
         <v>1</v>
       </c>
@@ -2126,8 +2224,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="17"/>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" s="19"/>
       <c r="B67" s="2">
         <v>2</v>
       </c>
@@ -2138,8 +2236,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="17">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" s="19">
         <v>543</v>
       </c>
       <c r="B68" s="2">
@@ -2155,8 +2253,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="17"/>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" s="19"/>
       <c r="B69" s="2">
         <v>1</v>
       </c>
@@ -2170,8 +2268,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="17"/>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" s="19"/>
       <c r="B70" s="2">
         <v>2</v>
       </c>
@@ -2185,8 +2283,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="17">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="19">
         <v>544</v>
       </c>
       <c r="B71" s="2">
@@ -2202,8 +2300,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="17"/>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="19"/>
       <c r="B72" s="2">
         <v>1</v>
       </c>
@@ -2217,8 +2315,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="17"/>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" s="19"/>
       <c r="B73" s="2">
         <v>2</v>
       </c>
@@ -2232,8 +2330,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="17">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" s="19">
         <v>545</v>
       </c>
       <c r="B74" s="2">
@@ -2249,8 +2347,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="17"/>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="19"/>
       <c r="B75" s="2">
         <v>1</v>
       </c>
@@ -2264,8 +2362,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="17"/>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" s="19"/>
       <c r="B76" s="2">
         <v>2</v>
       </c>
@@ -2279,8 +2377,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="17">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" s="19">
         <v>647</v>
       </c>
       <c r="B77" s="2">
@@ -2296,8 +2394,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="17"/>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" s="19"/>
       <c r="B78" s="2">
         <v>1</v>
       </c>
@@ -2311,8 +2409,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="17"/>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" s="19"/>
       <c r="B79" s="2">
         <v>2</v>
       </c>
@@ -2326,8 +2424,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="17">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" s="19">
         <v>648</v>
       </c>
       <c r="B80" s="2">
@@ -2343,8 +2441,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="17"/>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" s="19"/>
       <c r="B81" s="2">
         <v>1</v>
       </c>
@@ -2358,8 +2456,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="17"/>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" s="19"/>
       <c r="B82" s="2">
         <v>2</v>
       </c>
@@ -2373,8 +2471,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="17">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" s="19">
         <v>160</v>
       </c>
       <c r="B83" s="2">
@@ -2388,8 +2486,8 @@
       </c>
       <c r="E83" s="5"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="17"/>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84" s="19"/>
       <c r="B84" s="2">
         <v>1</v>
       </c>
@@ -2401,8 +2499,8 @@
       </c>
       <c r="E84" s="5"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="17"/>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" s="19"/>
       <c r="B85" s="2">
         <v>2</v>
       </c>
@@ -2414,8 +2512,8 @@
       </c>
       <c r="E85" s="5"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="17">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" s="19">
         <v>161</v>
       </c>
       <c r="B86" s="2">
@@ -2429,8 +2527,8 @@
       </c>
       <c r="E86" s="5"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="17"/>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" s="19"/>
       <c r="B87" s="2">
         <v>1</v>
       </c>
@@ -2442,8 +2540,8 @@
       </c>
       <c r="E87" s="5"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="17"/>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" s="19"/>
       <c r="B88" s="2">
         <v>2</v>
       </c>
@@ -2455,8 +2553,8 @@
       </c>
       <c r="E88" s="5"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="17">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" s="19">
         <v>162</v>
       </c>
       <c r="B89" s="2">
@@ -2470,8 +2568,8 @@
       </c>
       <c r="E89" s="5"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="17"/>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" s="19"/>
       <c r="B90" s="2">
         <v>1</v>
       </c>
@@ -2483,8 +2581,8 @@
       </c>
       <c r="E90" s="5"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="17"/>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" s="19"/>
       <c r="B91" s="2">
         <v>2</v>
       </c>
@@ -2496,8 +2594,8 @@
       </c>
       <c r="E91" s="5"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="17">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92" s="19">
         <v>163</v>
       </c>
       <c r="B92" s="2">
@@ -2511,8 +2609,8 @@
       </c>
       <c r="E92" s="5"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="17"/>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93" s="19"/>
       <c r="B93" s="2">
         <v>1</v>
       </c>
@@ -2524,8 +2622,8 @@
       </c>
       <c r="E93" s="5"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="17"/>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94" s="19"/>
       <c r="B94" s="2">
         <v>2</v>
       </c>
@@ -2537,8 +2635,8 @@
       </c>
       <c r="E94" s="5"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="17">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95" s="19">
         <v>116</v>
       </c>
       <c r="B95" s="2">
@@ -2552,8 +2650,8 @@
       </c>
       <c r="E95" s="5"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="17"/>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96" s="19"/>
       <c r="B96" s="2">
         <v>1</v>
       </c>
@@ -2565,8 +2663,8 @@
       </c>
       <c r="E96" s="5"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="17"/>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97" s="19"/>
       <c r="B97" s="2">
         <v>2</v>
       </c>
@@ -2578,8 +2676,8 @@
       </c>
       <c r="E97" s="5"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="17">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98" s="19">
         <v>117</v>
       </c>
       <c r="B98" s="2">
@@ -2593,8 +2691,8 @@
       </c>
       <c r="E98" s="5"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="17"/>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99" s="19"/>
       <c r="B99" s="2">
         <v>1</v>
       </c>
@@ -2606,8 +2704,8 @@
       </c>
       <c r="E99" s="5"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="17"/>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100" s="19"/>
       <c r="B100" s="2">
         <v>2</v>
       </c>
@@ -2619,8 +2717,8 @@
       </c>
       <c r="E100" s="5"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="17">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101" s="19">
         <v>118</v>
       </c>
       <c r="B101" s="2">
@@ -2634,8 +2732,8 @@
       </c>
       <c r="E101" s="5"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="17"/>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102" s="19"/>
       <c r="B102" s="2">
         <v>1</v>
       </c>
@@ -2647,8 +2745,8 @@
       </c>
       <c r="E102" s="5"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="17"/>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103" s="19"/>
       <c r="B103" s="2">
         <v>2</v>
       </c>
@@ -2660,8 +2758,8 @@
       </c>
       <c r="E103" s="5"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="17">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104" s="19">
         <v>119</v>
       </c>
       <c r="B104" s="2">
@@ -2675,8 +2773,8 @@
       </c>
       <c r="E104" s="5"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="17"/>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105" s="19"/>
       <c r="B105" s="2">
         <v>1</v>
       </c>
@@ -2687,8 +2785,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="17"/>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106" s="19"/>
       <c r="B106" s="2">
         <v>2</v>
       </c>
@@ -2699,8 +2797,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="17">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107" s="19">
         <v>120</v>
       </c>
       <c r="B107" s="2">
@@ -2713,8 +2811,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="17"/>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" s="19"/>
       <c r="B108" s="2">
         <v>1</v>
       </c>
@@ -2725,8 +2823,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="17"/>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" s="19"/>
       <c r="B109" s="2">
         <v>2</v>
       </c>
@@ -2737,8 +2835,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="17">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" s="19">
         <v>121</v>
       </c>
       <c r="B110" s="2">
@@ -2751,8 +2849,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="17"/>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" s="19"/>
       <c r="B111" s="2">
         <v>1</v>
       </c>
@@ -2763,8 +2861,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="17"/>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112" s="19"/>
       <c r="B112" s="2">
         <v>2</v>
       </c>
@@ -2775,8 +2873,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="17">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" s="19">
         <v>136</v>
       </c>
       <c r="B113" s="2">
@@ -2789,8 +2887,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="17"/>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" s="19"/>
       <c r="B114" s="2">
         <v>1</v>
       </c>
@@ -2801,8 +2899,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="17"/>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" s="19"/>
       <c r="B115" s="2">
         <v>2</v>
       </c>
@@ -2813,8 +2911,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="17">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" s="19">
         <v>137</v>
       </c>
       <c r="B116" s="2">
@@ -2827,8 +2925,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="17"/>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" s="19"/>
       <c r="B117" s="2">
         <v>1</v>
       </c>
@@ -2839,8 +2937,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="17"/>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118" s="19"/>
       <c r="B118" s="2">
         <v>2</v>
       </c>
@@ -2851,8 +2949,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="17">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" s="19">
         <v>206</v>
       </c>
       <c r="B119" s="2">
@@ -2865,8 +2963,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="17"/>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" s="19"/>
       <c r="B120" s="2">
         <v>1</v>
       </c>
@@ -2877,8 +2975,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="17"/>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" s="19"/>
       <c r="B121" s="2">
         <v>2</v>
       </c>
@@ -2889,8 +2987,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="17">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" s="19">
         <v>207</v>
       </c>
       <c r="B122" s="2">
@@ -2903,8 +3001,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="17"/>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" s="19"/>
       <c r="B123" s="2">
         <v>1</v>
       </c>
@@ -2915,8 +3013,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="17"/>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" s="19"/>
       <c r="B124" s="2">
         <v>2</v>
       </c>
@@ -2927,8 +3025,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="17">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" s="19">
         <v>210</v>
       </c>
       <c r="B125" s="2">
@@ -2941,8 +3039,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="17"/>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" s="19"/>
       <c r="B126" s="2">
         <v>1</v>
       </c>
@@ -2953,8 +3051,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="17"/>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" s="19"/>
       <c r="B127" s="2">
         <v>2</v>
       </c>
@@ -2965,8 +3063,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="17">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" s="19">
         <v>211</v>
       </c>
       <c r="B128" s="2">
@@ -2979,8 +3077,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="17"/>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129" s="19"/>
       <c r="B129" s="2">
         <v>1</v>
       </c>
@@ -2991,8 +3089,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="17"/>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A130" s="19"/>
       <c r="B130" s="2">
         <v>2</v>
       </c>
@@ -3003,7 +3101,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="18">
         <v>666</v>
       </c>
@@ -3020,7 +3118,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="18"/>
       <c r="B132" s="11">
         <v>1</v>
@@ -3035,7 +3133,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="18"/>
       <c r="B133" s="11">
         <v>2</v>
@@ -3050,7 +3148,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="18">
         <v>667</v>
       </c>
@@ -3067,7 +3165,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="18"/>
       <c r="B135" s="11">
         <v>1</v>
@@ -3082,7 +3180,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="18"/>
       <c r="B136" s="11">
         <v>2</v>
@@ -3097,7 +3195,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="18">
         <v>668</v>
       </c>
@@ -3114,7 +3212,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="18"/>
       <c r="B138" s="11">
         <v>1</v>
@@ -3129,7 +3227,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="18"/>
       <c r="B139" s="11">
         <v>2</v>
@@ -3144,7 +3242,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="18">
         <v>669</v>
       </c>
@@ -3161,7 +3259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="18"/>
       <c r="B141" s="11">
         <v>1</v>
@@ -3176,7 +3274,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="18"/>
       <c r="B142" s="11">
         <v>2</v>
@@ -3191,7 +3289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="18">
         <v>670</v>
       </c>
@@ -3208,7 +3306,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="18"/>
       <c r="B144" s="11">
         <v>1</v>
@@ -3223,7 +3321,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="18"/>
       <c r="B145" s="11">
         <v>2</v>
@@ -3238,7 +3336,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="18">
         <v>671</v>
       </c>
@@ -3255,7 +3353,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="18"/>
       <c r="B147" s="11">
         <v>1</v>
@@ -3270,7 +3368,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="18"/>
       <c r="B148" s="11">
         <v>2</v>
@@ -3285,14 +3383,285 @@
         <v>32</v>
       </c>
     </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A149" s="18">
+        <v>845</v>
+      </c>
+      <c r="B149" s="17">
+        <v>0</v>
+      </c>
+      <c r="C149" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D149" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E149" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A150" s="18"/>
+      <c r="B150" s="17">
+        <v>1</v>
+      </c>
+      <c r="C150" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D150" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E150" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A151" s="18"/>
+      <c r="B151" s="17">
+        <v>2</v>
+      </c>
+      <c r="C151" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D151" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E151" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A152" s="18">
+        <v>846</v>
+      </c>
+      <c r="B152" s="17">
+        <v>0</v>
+      </c>
+      <c r="C152" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D152" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E152" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A153" s="18"/>
+      <c r="B153" s="17">
+        <v>1</v>
+      </c>
+      <c r="C153" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D153" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E153" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A154" s="18"/>
+      <c r="B154" s="17">
+        <v>2</v>
+      </c>
+      <c r="C154" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D154" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E154" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A155" s="18">
+        <v>847</v>
+      </c>
+      <c r="B155" s="17">
+        <v>0</v>
+      </c>
+      <c r="C155" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D155" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E155" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A156" s="18"/>
+      <c r="B156" s="17">
+        <v>1</v>
+      </c>
+      <c r="C156" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D156" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E156" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A157" s="18"/>
+      <c r="B157" s="17">
+        <v>2</v>
+      </c>
+      <c r="C157" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D157" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E157" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A158" s="18">
+        <v>19103</v>
+      </c>
+      <c r="B158" s="17">
+        <v>0</v>
+      </c>
+      <c r="C158" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D158" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E158" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A159" s="18"/>
+      <c r="B159" s="17">
+        <v>1</v>
+      </c>
+      <c r="C159" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D159" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E159" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A160" s="18"/>
+      <c r="B160" s="17">
+        <v>2</v>
+      </c>
+      <c r="C160" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D160" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E160" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A161" s="18">
+        <v>19105</v>
+      </c>
+      <c r="B161" s="17">
+        <v>0</v>
+      </c>
+      <c r="C161" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D161" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E161" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A162" s="18"/>
+      <c r="B162" s="17">
+        <v>1</v>
+      </c>
+      <c r="C162" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D162" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E162" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A163" s="18"/>
+      <c r="B163" s="17">
+        <v>2</v>
+      </c>
+      <c r="C163" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D163" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E163" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="A143:A145"/>
+  <mergeCells count="55">
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="A107:A109"/>
     <mergeCell ref="A125:A127"/>
     <mergeCell ref="A128:A130"/>
     <mergeCell ref="A110:A112"/>
@@ -3300,43 +3669,12 @@
     <mergeCell ref="A116:A118"/>
     <mergeCell ref="A119:A121"/>
     <mergeCell ref="A122:A124"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78750000000000009" bottom="0.78750000000000009" header="0.51181102362204689" footer="0.51181102362204689"/>
   <pageSetup paperSize="9" firstPageNumber="4294967295" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
